--- a/output/pdf_financials_xlsx/WIN.xlsx
+++ b/output/pdf_financials_xlsx/WIN.xlsx
@@ -616,10 +616,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.008332000000000001</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.009863</v>
       </c>
     </row>
     <row r="13">
@@ -874,10 +874,10 @@
         <v>-1.522846</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.925249</v>
+        <v>-0.933581</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.173332</v>
+        <v>-1.183195</v>
       </c>
     </row>
     <row r="28">
@@ -906,10 +906,10 @@
         <v>-1.534387</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.925249</v>
+        <v>-0.933581</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.173332</v>
+        <v>-1.183195</v>
       </c>
     </row>
     <row r="30">
@@ -986,13 +986,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.331383</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.017551</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.180958</v>
       </c>
     </row>
     <row r="35">
@@ -1018,13 +1018,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.634538</v>
+        <v>0.965921</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.138175</v>
+        <v>0.155726</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.035</v>
+        <v>0.215958</v>
       </c>
     </row>
     <row r="37">
@@ -1210,13 +1210,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.366448</v>
+        <v>0.035065</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.024402</v>
+        <v>0.006851</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.186369</v>
+        <v>0.005411</v>
       </c>
     </row>
     <row r="49">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">

--- a/output/pdf_financials_xlsx/WIN.xlsx
+++ b/output/pdf_financials_xlsx/WIN.xlsx
@@ -1472,13 +1472,13 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.052945</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.180099</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.211618</v>
       </c>
     </row>
     <row r="65">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.0375</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.158368</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.140528</v>
       </c>
     </row>
     <row r="68">
@@ -2287,7 +2287,7 @@
         <v>0</v>
       </c>
       <c r="D114" s="3" t="n">
-        <v>0</v>
+        <v>-0.025</v>
       </c>
     </row>
     <row r="115">
@@ -3927,7 +3927,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
